--- a/src/main/java/ExcelDriven/excelDriven.xlsx
+++ b/src/main/java/ExcelDriven/excelDriven.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBD783C-974A-AB44-8BFF-F24113BF4DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB45734-08AE-E245-9A33-6ABD2B8FB6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="-28200" windowWidth="20000" windowHeight="16540" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Greeting</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>AS</t>
   </si>
 </sst>
 </file>
@@ -488,8 +491,8 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">

--- a/src/main/java/ExcelDriven/excelDriven.xlsx
+++ b/src/main/java/ExcelDriven/excelDriven.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB45734-08AE-E245-9A33-6ABD2B8FB6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B330CA07-6E1C-864D-ACB8-864CB0D6CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="-28200" windowWidth="20000" windowHeight="16540" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
+    <workbookView xWindow="3020" yWindow="2200" windowWidth="22980" windowHeight="15980" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Greeting</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <t>AS</t>
+  </si>
+  <si>
+    <t>12SD</t>
+  </si>
+  <si>
+    <t>14SD</t>
   </si>
 </sst>
 </file>
@@ -502,8 +508,8 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
-        <v>143</v>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -513,8 +519,8 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
-        <v>453</v>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/ExcelDriven/excelDriven.xlsx
+++ b/src/main/java/ExcelDriven/excelDriven.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B330CA07-6E1C-864D-ACB8-864CB0D6CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E416C-96A9-BD45-889B-ACF24B61E077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3020" yWindow="2200" windowWidth="22980" windowHeight="15980" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
+    <workbookView xWindow="7340" yWindow="5500" windowWidth="22980" windowHeight="15980" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Greeting</t>
   </si>
@@ -63,15 +63,6 @@
   </si>
   <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>AS</t>
-  </si>
-  <si>
-    <t>12SD</t>
-  </si>
-  <si>
-    <t>14SD</t>
   </si>
 </sst>
 </file>
@@ -497,8 +488,8 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
+      <c r="C2" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -508,8 +499,8 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
+      <c r="C3" s="1">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -519,8 +510,8 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
+      <c r="C4" s="1">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/ExcelDriven/excelDriven.xlsx
+++ b/src/main/java/ExcelDriven/excelDriven.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/ExcelDriven/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Document-Local/Documents/Development_Local/Selenium_Java_TestNG_CICD/src/main/java/ExcelDriven/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76E416C-96A9-BD45-889B-ACF24B61E077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F1C302-94F3-8A49-9450-D0E4959C4802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7340" yWindow="5500" windowWidth="22980" windowHeight="15980" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
+    <workbookView xWindow="6480" yWindow="2380" windowWidth="22980" windowHeight="15980" xr2:uid="{CC656AC3-E306-AE44-BCD5-BDE430834125}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -489,7 +489,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="1">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -500,7 +500,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -511,7 +511,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>33</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
